--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_MEDIL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_MEDIL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε_2026-02.xlsx
@@ -2844,7 +2844,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
